--- a/artfynd/A 15379-2024 artfynd.xlsx
+++ b/artfynd/A 15379-2024 artfynd.xlsx
@@ -1374,7 +1374,7 @@
         <v>117771810</v>
       </c>
       <c r="B8" t="n">
-        <v>97742</v>
+        <v>97744</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 15379-2024 artfynd.xlsx
+++ b/artfynd/A 15379-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>104025019</v>
+        <v>117771810</v>
       </c>
       <c r="B2" t="n">
-        <v>90319</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99024</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,41 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4769</v>
+        <v>504</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>V Rödmyran, Jmt</t>
+          <t>Selsviken, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>548375.1997925093</v>
+        <v>548340</v>
       </c>
       <c r="R2" t="n">
-        <v>7007092.205979335</v>
+        <v>7007107</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +744,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-08-19</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>14:44</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-08-19</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>14:44</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,31 +764,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Amanda Evensen</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Amanda Evensen, Noel Wieser</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>104025020</v>
+        <v>127012864</v>
       </c>
       <c r="B3" t="n">
-        <v>95661</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99024</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,34 +787,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222741</v>
+        <v>504</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>V Rödmyran, Jmt</t>
+          <t>Rödmyran, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>548325.3904284589</v>
+        <v>548409</v>
       </c>
       <c r="R3" t="n">
-        <v>7007006.575745064</v>
+        <v>7007127</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -861,22 +841,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-08-19</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>14:28</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-08-19</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>14:28</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -891,69 +861,63 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Clara Lerbro</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Clara Lerbro</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>104025018</v>
+        <v>117899760</v>
       </c>
       <c r="B4" t="n">
-        <v>95661</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92083</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222741</v>
+        <v>1503</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>V Rödmyran, Jmt</t>
+          <t>Selsviken, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>548352.9235192268</v>
+        <v>548555</v>
       </c>
       <c r="R4" t="n">
-        <v>7007039.948566237</v>
+        <v>7006812</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -977,22 +941,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-08-19</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>14:41</t>
+          <t>2024-06-15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-08-19</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>14:41</t>
+          <t>2024-06-15</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1001,59 +955,51 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Amanda Evensen</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Amanda Evensen</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>104025017</v>
+        <v>104025019</v>
       </c>
       <c r="B5" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>4769</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1063,10 +1009,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>548357.1810346182</v>
+        <v>548375</v>
       </c>
       <c r="R5" t="n">
-        <v>7007027.369835543</v>
+        <v>7007092</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1098,7 +1044,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1108,7 +1054,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,50 +1085,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>104025016</v>
+        <v>127012865</v>
       </c>
       <c r="B6" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>V Rödmyran, Jmt</t>
+          <t>Rödmyran, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>548364.4306447331</v>
+        <v>548409</v>
       </c>
       <c r="R6" t="n">
-        <v>7007147.128281016</v>
+        <v>7007127</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1209,22 +1150,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-08-19</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>14:45</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-08-19</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>14:45</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1239,66 +1170,57 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Clara Lerbro</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Clara Lerbro</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>104025021</v>
+        <v>104025028</v>
       </c>
       <c r="B7" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99142</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>219847</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>V Rödmyran, Jmt</t>
+          <t>Norr Selsviken, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>548535.2360882785</v>
+        <v>548553</v>
       </c>
       <c r="R7" t="n">
-        <v>7006852.588831146</v>
+        <v>7006823</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1330,7 +1252,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1340,7 +1262,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1371,57 +1293,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117771810</v>
+        <v>104025017</v>
       </c>
       <c r="B8" t="n">
-        <v>97746</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>504</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Selsviken, Jmt</t>
+          <t>V Rödmyran, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>548340</v>
+        <v>548357</v>
       </c>
       <c r="R8" t="n">
-        <v>7007107</v>
+        <v>7007027</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1445,12 +1358,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>2022-08-19</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>2022-08-19</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1465,15 +1388,574 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Amanda Evensen</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Amanda Evensen, Noel Wieser</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>104025021</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>V Rödmyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>548535</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7006852</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2022-08-19</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2022-08-19</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>104025016</v>
+      </c>
+      <c r="B10" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>V Rödmyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>548365</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7007147</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2022-08-19</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2022-08-19</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>104025018</v>
+      </c>
+      <c r="B11" t="n">
+        <v>98137</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>222741</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Finbräken</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Cystopteris montana</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Lam.) Desv.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>V Rödmyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>548353</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7007040</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2022-08-19</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>14:41</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2022-08-19</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>14:41</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>104025020</v>
+      </c>
+      <c r="B12" t="n">
+        <v>98137</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>222741</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Finbräken</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Cystopteris montana</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Lam.) Desv.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>V Rödmyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>548325</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7007007</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2022-08-19</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2022-08-19</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>104025029</v>
+      </c>
+      <c r="B13" t="n">
+        <v>98137</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>222741</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Finbräken</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Cystopteris montana</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Lam.) Desv.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Norr Selsviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>548559</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7006824</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2022-08-19</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>13:37</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2022-08-19</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>13:37</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 15379-2024 artfynd.xlsx
+++ b/artfynd/A 15379-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117771810</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -870,6 +880,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127012864</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -971,6 +986,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117899760</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1082,6 +1102,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104025019</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1179,6 +1204,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127012865</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1290,6 +1320,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104025028</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1401,6 +1436,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104025017</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1512,6 +1552,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104025021</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1623,6 +1668,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104025016</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1734,6 +1784,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104025018</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1845,6 +1900,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104025020</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1956,8 +2016,27 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104025029</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>